--- a/workbook/Dang-accounting-prototype.xlsx
+++ b/workbook/Dang-accounting-prototype.xlsx
@@ -276,7 +276,7 @@
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Dong</author>
+    <author>Dang</author>
   </authors>
   <commentList>
     <comment ref="B8" authorId="0" shapeId="0">
